--- a/artfynd/A 19250-2026 artfynd.xlsx
+++ b/artfynd/A 19250-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11471,6 +11471,236 @@
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>132917305</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Movisen V, Valö, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>667801</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6691915</v>
+      </c>
+      <c r="S107" t="n">
+        <v>25</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>132917355</v>
+      </c>
+      <c r="B108" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Movisen V2, Valö, Upl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>667794</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6691808</v>
+      </c>
+      <c r="S108" t="n">
+        <v>25</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19250-2026 artfynd.xlsx
+++ b/artfynd/A 19250-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121373647</v>
+        <v>125807855</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667840</v>
+        <v>668099</v>
       </c>
       <c r="R2" t="n">
-        <v>6691700</v>
+        <v>6691799</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +772,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125807858</v>
+        <v>125807884</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668168</v>
+        <v>667915</v>
       </c>
       <c r="R3" t="n">
-        <v>6691761</v>
+        <v>6691901</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -861,23 +863,9 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125807894</v>
+        <v>125807870</v>
       </c>
       <c r="B4" t="n">
-        <v>4778</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667740</v>
+        <v>668161</v>
       </c>
       <c r="R4" t="n">
-        <v>6691828</v>
+        <v>6691754</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1009,7 +997,7 @@
         <v>125807871</v>
       </c>
       <c r="B5" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,12 +1014,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1118,45 +1106,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125807891</v>
+        <v>127382957</v>
       </c>
       <c r="B6" t="n">
-        <v>4778</v>
+        <v>92147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>1101</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>667961</v>
+        <v>668028</v>
       </c>
       <c r="R6" t="n">
-        <v>6691858</v>
+        <v>6691913</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,12 +1171,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,54 +1218,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125807878</v>
+        <v>125807858</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668030</v>
+        <v>668168</v>
       </c>
       <c r="R7" t="n">
-        <v>6691905</v>
+        <v>6691761</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1312,11 +1291,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vid stenblock</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1325,6 +1299,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1341,32 +1330,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125807879</v>
+        <v>125807859</v>
       </c>
       <c r="B8" t="n">
-        <v>75014</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668003</v>
+        <v>668120</v>
       </c>
       <c r="R8" t="n">
-        <v>6691888</v>
+        <v>6691780</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1453,32 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125807907</v>
+        <v>125807861</v>
       </c>
       <c r="B9" t="n">
-        <v>100543</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1488,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>667915</v>
+        <v>668036</v>
       </c>
       <c r="R9" t="n">
-        <v>6691893</v>
+        <v>6691909</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1534,6 +1523,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1550,32 +1554,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125807904</v>
+        <v>125807862</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>667959</v>
+        <v>667988</v>
       </c>
       <c r="R10" t="n">
-        <v>6691856</v>
+        <v>6691887</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1662,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125807864</v>
+        <v>125807863</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>667880</v>
+        <v>667929</v>
       </c>
       <c r="R11" t="n">
-        <v>6691878</v>
+        <v>6691852</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1774,32 +1778,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125807880</v>
+        <v>125807864</v>
       </c>
       <c r="B12" t="n">
-        <v>75014</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1809,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>667963</v>
+        <v>667880</v>
       </c>
       <c r="R12" t="n">
-        <v>6691870</v>
+        <v>6691878</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1886,54 +1890,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125807883</v>
+        <v>125832163</v>
       </c>
       <c r="B13" t="n">
-        <v>105396</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668026</v>
+        <v>668118</v>
       </c>
       <c r="R13" t="n">
-        <v>6691901</v>
+        <v>6691779</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1980,44 +1975,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125807902</v>
+        <v>125855884</v>
       </c>
       <c r="B14" t="n">
-        <v>5176</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,13 +2022,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668094</v>
+        <v>667920</v>
       </c>
       <c r="R14" t="n">
-        <v>6691828</v>
+        <v>6691789</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,41 +2068,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125807870</v>
+        <v>125855886</v>
       </c>
       <c r="B15" t="n">
-        <v>91541</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2139,13 +2119,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668161</v>
+        <v>667883</v>
       </c>
       <c r="R15" t="n">
-        <v>6691754</v>
+        <v>6691862</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2185,41 +2165,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125807861</v>
+        <v>125984221</v>
       </c>
       <c r="B16" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,13 +2216,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668036</v>
+        <v>668119</v>
       </c>
       <c r="R16" t="n">
-        <v>6691909</v>
+        <v>6691778</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2297,41 +2262,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125807855</v>
+        <v>125984222</v>
       </c>
       <c r="B17" t="n">
-        <v>96614</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2289,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2313,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668099</v>
+        <v>668081</v>
       </c>
       <c r="R17" t="n">
-        <v>6691799</v>
+        <v>6691773</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,72 +2363,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125807884</v>
+        <v>125984223</v>
       </c>
       <c r="B18" t="n">
-        <v>95810</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>667915</v>
+        <v>667997</v>
       </c>
       <c r="R18" t="n">
-        <v>6691901</v>
+        <v>6691842</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,51 +2454,50 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125807896</v>
+        <v>125984224</v>
       </c>
       <c r="B19" t="n">
-        <v>4778</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,13 +2507,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>667759</v>
+        <v>667842</v>
       </c>
       <c r="R19" t="n">
-        <v>6691753</v>
+        <v>6691878</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2616,76 +2553,61 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125807892</v>
+        <v>127382932</v>
       </c>
       <c r="B20" t="n">
-        <v>4778</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>667736</v>
+        <v>667928</v>
       </c>
       <c r="R20" t="n">
-        <v>6691854</v>
+        <v>6691781</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2712,12 +2634,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2759,45 +2681,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125807882</v>
+        <v>127382933</v>
       </c>
       <c r="B21" t="n">
-        <v>75014</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>667748</v>
+        <v>668060</v>
       </c>
       <c r="R21" t="n">
-        <v>6691840</v>
+        <v>6691824</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2824,12 +2746,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,32 +2793,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125807905</v>
+        <v>125984234</v>
       </c>
       <c r="B22" t="n">
-        <v>5176</v>
+        <v>92369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2906,13 +2828,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>667721</v>
+        <v>668124</v>
       </c>
       <c r="R22" t="n">
-        <v>6691796</v>
+        <v>6691768</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2952,76 +2874,61 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125807886</v>
+        <v>127382965</v>
       </c>
       <c r="B23" t="n">
-        <v>91263</v>
+        <v>92564</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1339</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668028</v>
+        <v>667915</v>
       </c>
       <c r="R23" t="n">
-        <v>6691902</v>
+        <v>6691881</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3048,12 +2955,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3067,17 +2974,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3095,45 +3002,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125807859</v>
+        <v>127382946</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>91680</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668120</v>
+        <v>667937</v>
       </c>
       <c r="R24" t="n">
-        <v>6691780</v>
+        <v>6691781</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3160,12 +3067,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,21 +3083,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3207,10 +3099,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125807857</v>
+        <v>127382947</v>
       </c>
       <c r="B25" t="n">
-        <v>91210</v>
+        <v>91680</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,34 +3110,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667996</v>
+        <v>667947</v>
       </c>
       <c r="R25" t="n">
-        <v>6691895</v>
+        <v>6691871</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3272,12 +3164,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,21 +3180,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3319,10 +3196,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125807881</v>
+        <v>128260559</v>
       </c>
       <c r="B26" t="n">
-        <v>75014</v>
+        <v>91680</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3330,37 +3207,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667958</v>
+        <v>667946</v>
       </c>
       <c r="R26" t="n">
-        <v>6691859</v>
+        <v>6691856</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3384,12 +3261,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3400,21 +3277,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3431,10 +3293,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125807890</v>
+        <v>128260560</v>
       </c>
       <c r="B27" t="n">
-        <v>4778</v>
+        <v>91680</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3442,37 +3304,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>3215</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668014</v>
+        <v>667935</v>
       </c>
       <c r="R27" t="n">
-        <v>6691884</v>
+        <v>6691779</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3496,12 +3358,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,21 +3374,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3543,48 +3390,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125807895</v>
+        <v>128260587</v>
       </c>
       <c r="B28" t="n">
-        <v>4778</v>
+        <v>91361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>3286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>667743</v>
+        <v>667939</v>
       </c>
       <c r="R28" t="n">
-        <v>6691820</v>
+        <v>6691912</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3608,12 +3455,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3624,21 +3471,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3655,45 +3487,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125807906</v>
+        <v>127382944</v>
       </c>
       <c r="B29" t="n">
-        <v>100543</v>
+        <v>93209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>667888</v>
+        <v>667983</v>
       </c>
       <c r="R29" t="n">
-        <v>6691884</v>
+        <v>6691868</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3720,12 +3552,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3752,10 +3584,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125807863</v>
+        <v>127382945</v>
       </c>
       <c r="B30" t="n">
-        <v>91245</v>
+        <v>93209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3763,34 +3595,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>667929</v>
+        <v>667937</v>
       </c>
       <c r="R30" t="n">
-        <v>6691852</v>
+        <v>6691815</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3817,12 +3649,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3833,21 +3665,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3864,48 +3681,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125832166</v>
+        <v>128260553</v>
       </c>
       <c r="B31" t="n">
-        <v>75014</v>
+        <v>93209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668116</v>
+        <v>667943</v>
       </c>
       <c r="R31" t="n">
-        <v>6691883</v>
+        <v>6691900</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3929,12 +3746,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,57 +3766,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125832167</v>
+        <v>127382962</v>
       </c>
       <c r="B32" t="n">
-        <v>105396</v>
+        <v>93215</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>667940</v>
+        <v>667935</v>
       </c>
       <c r="R32" t="n">
-        <v>6691828</v>
+        <v>6691764</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4026,12 +3843,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4046,22 +3863,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125832160</v>
+        <v>128260589</v>
       </c>
       <c r="B33" t="n">
-        <v>75075</v>
+        <v>93215</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4069,37 +3886,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>4368</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668116</v>
+        <v>667928</v>
       </c>
       <c r="R33" t="n">
-        <v>6691879</v>
+        <v>6691772</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4123,12 +3940,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4143,22 +3960,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125832164</v>
+        <v>127382938</v>
       </c>
       <c r="B34" t="n">
-        <v>56849</v>
+        <v>92869</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,34 +3983,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668112</v>
+        <v>667939</v>
       </c>
       <c r="R34" t="n">
-        <v>6691817</v>
+        <v>6691746</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4220,12 +4037,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4240,60 +4057,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125832163</v>
+        <v>128260544</v>
       </c>
       <c r="B35" t="n">
-        <v>91245</v>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668118</v>
+        <v>667938</v>
       </c>
       <c r="R35" t="n">
-        <v>6691779</v>
+        <v>6691896</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4317,12 +4134,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4337,22 +4154,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125832173</v>
+        <v>128260545</v>
       </c>
       <c r="B36" t="n">
-        <v>100543</v>
+        <v>92869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4360,37 +4177,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668118</v>
+        <v>667945</v>
       </c>
       <c r="R36" t="n">
-        <v>6691903</v>
+        <v>6691836</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4414,12 +4231,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4434,22 +4251,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125832165</v>
+        <v>128260547</v>
       </c>
       <c r="B37" t="n">
-        <v>56849</v>
+        <v>92869</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4457,37 +4274,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>667750</v>
+        <v>667935</v>
       </c>
       <c r="R37" t="n">
-        <v>6691766</v>
+        <v>6691779</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4511,17 +4328,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Spillning på hällhöjd</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4536,22 +4348,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125855909</v>
+        <v>125807857</v>
       </c>
       <c r="B38" t="n">
-        <v>105396</v>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4559,21 +4371,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4583,13 +4395,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>667931</v>
+        <v>667996</v>
       </c>
       <c r="R38" t="n">
-        <v>6691727</v>
+        <v>6691895</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4629,26 +4441,41 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125855924</v>
+        <v>125984217</v>
       </c>
       <c r="B39" t="n">
-        <v>98278</v>
+        <v>91872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4656,21 +4483,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4680,10 +4507,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>667949</v>
+        <v>668042</v>
       </c>
       <c r="R39" t="n">
-        <v>6691737</v>
+        <v>6691903</v>
       </c>
       <c r="S39" t="n">
         <v>12</v>
@@ -4730,22 +4557,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125855900</v>
+        <v>125984218</v>
       </c>
       <c r="B40" t="n">
-        <v>97239</v>
+        <v>91872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,21 +4580,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4777,10 +4604,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668113</v>
+        <v>667998</v>
       </c>
       <c r="R40" t="n">
-        <v>6691886</v>
+        <v>6691845</v>
       </c>
       <c r="S40" t="n">
         <v>12</v>
@@ -4827,22 +4654,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125853671</v>
+        <v>127382929</v>
       </c>
       <c r="B41" t="n">
-        <v>4778</v>
+        <v>91872</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4850,37 +4677,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668108</v>
+        <v>668059</v>
       </c>
       <c r="R41" t="n">
-        <v>6691869</v>
+        <v>6691834</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4904,12 +4731,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4920,26 +4747,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125855897</v>
+        <v>127382930</v>
       </c>
       <c r="B42" t="n">
-        <v>56849</v>
+        <v>91872</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4947,45 +4789,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>667812</v>
+        <v>668026</v>
       </c>
       <c r="R42" t="n">
-        <v>6691902</v>
+        <v>6691913</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5009,12 +4843,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5025,48 +4859,63 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125855918</v>
+        <v>125807879</v>
       </c>
       <c r="B43" t="n">
-        <v>98278</v>
+        <v>75428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5076,13 +4925,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668099</v>
+        <v>668003</v>
       </c>
       <c r="R43" t="n">
-        <v>6691912</v>
+        <v>6691888</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5122,64 +4971,79 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125853675</v>
+        <v>125807880</v>
       </c>
       <c r="B44" t="n">
-        <v>98278</v>
+        <v>75428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668105</v>
+        <v>667963</v>
       </c>
       <c r="R44" t="n">
-        <v>6691791</v>
+        <v>6691870</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5219,48 +5083,63 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125855929</v>
+        <v>125807881</v>
       </c>
       <c r="B45" t="n">
-        <v>98278</v>
+        <v>75428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5270,13 +5149,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>667863</v>
+        <v>667958</v>
       </c>
       <c r="R45" t="n">
-        <v>6691900</v>
+        <v>6691859</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5316,72 +5195,79 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125855899</v>
+        <v>125807882</v>
       </c>
       <c r="B46" t="n">
-        <v>56849</v>
+        <v>75428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>667772</v>
+        <v>667748</v>
       </c>
       <c r="R46" t="n">
-        <v>6691729</v>
+        <v>6691840</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5413,11 +5299,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färsk spillning. På häll. En del kortklippta med vitt. Eventuellt spelspillning.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5426,72 +5307,79 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125855892</v>
+        <v>125832166</v>
       </c>
       <c r="B47" t="n">
-        <v>56849</v>
+        <v>75428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>667883</v>
+        <v>668116</v>
       </c>
       <c r="R47" t="n">
-        <v>6691737</v>
+        <v>6691883</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5521,11 +5409,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färsk spillning, riklig</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5540,44 +5423,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125855921</v>
+        <v>125832160</v>
       </c>
       <c r="B48" t="n">
-        <v>98278</v>
+        <v>83307</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5587,13 +5470,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>667940</v>
+        <v>668116</v>
       </c>
       <c r="R48" t="n">
-        <v>6691725</v>
+        <v>6691879</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5637,22 +5520,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125855927</v>
+        <v>121373647</v>
       </c>
       <c r="B49" t="n">
-        <v>98278</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5660,37 +5543,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>östensbo, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>667941</v>
+        <v>667840</v>
       </c>
       <c r="R49" t="n">
-        <v>6691897</v>
+        <v>6691700</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5714,12 +5602,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5734,22 +5622,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125853674</v>
+        <v>125853669</v>
       </c>
       <c r="B50" t="n">
-        <v>98278</v>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5757,21 +5645,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5781,10 +5669,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668118</v>
+        <v>667834</v>
       </c>
       <c r="R50" t="n">
-        <v>6691756</v>
+        <v>6691885</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -5843,10 +5731,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125855896</v>
+        <v>125853670</v>
       </c>
       <c r="B51" t="n">
-        <v>56849</v>
+        <v>57950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5854,45 +5742,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>667767</v>
+        <v>667799</v>
       </c>
       <c r="R51" t="n">
-        <v>6691898</v>
+        <v>6691867</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5936,22 +5816,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125853672</v>
+        <v>127382941</v>
       </c>
       <c r="B52" t="n">
-        <v>4778</v>
+        <v>57950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5959,37 +5839,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>667767</v>
+        <v>668038</v>
       </c>
       <c r="R52" t="n">
-        <v>6691757</v>
+        <v>6691921</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6013,12 +5898,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6033,26 +5918,26 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125853669</v>
+        <v>132917305</v>
       </c>
       <c r="B53" t="n">
-        <v>57654</v>
+        <v>57972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6074,19 +5959,27 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Movisen V, Valö, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667834</v>
+        <v>667801</v>
       </c>
       <c r="R53" t="n">
-        <v>6691885</v>
+        <v>6691915</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6110,12 +6003,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6130,22 +6033,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125855902</v>
+        <v>132917355</v>
       </c>
       <c r="B54" t="n">
-        <v>97239</v>
+        <v>57972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6153,37 +6056,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Movisen V2, Valö, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667921</v>
+        <v>667794</v>
       </c>
       <c r="R54" t="n">
-        <v>6691714</v>
+        <v>6691808</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6207,12 +6118,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6227,44 +6148,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125855884</v>
+        <v>125832164</v>
       </c>
       <c r="B55" t="n">
-        <v>91245</v>
+        <v>57141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6274,13 +6195,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>667920</v>
+        <v>668112</v>
       </c>
       <c r="R55" t="n">
-        <v>6691789</v>
+        <v>6691817</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6324,22 +6245,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125855930</v>
+        <v>125832165</v>
       </c>
       <c r="B56" t="n">
-        <v>100543</v>
+        <v>57141</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6347,21 +6268,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6371,13 +6292,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>667952</v>
+        <v>667750</v>
       </c>
       <c r="R56" t="n">
-        <v>6691797</v>
+        <v>6691766</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6407,6 +6328,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Spillning på hällhöjd</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6421,22 +6347,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125855922</v>
+        <v>125855892</v>
       </c>
       <c r="B57" t="n">
-        <v>98278</v>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6444,34 +6370,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>667907</v>
+        <v>667883</v>
       </c>
       <c r="R57" t="n">
-        <v>6691699</v>
+        <v>6691737</v>
       </c>
       <c r="S57" t="n">
         <v>12</v>
@@ -6504,6 +6438,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färsk spillning, riklig</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6530,10 +6469,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125855925</v>
+        <v>125855894</v>
       </c>
       <c r="B58" t="n">
-        <v>98278</v>
+        <v>57141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6541,34 +6480,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>667944</v>
+        <v>667874</v>
       </c>
       <c r="R58" t="n">
-        <v>6691755</v>
+        <v>6691937</v>
       </c>
       <c r="S58" t="n">
         <v>12</v>
@@ -6627,48 +6574,56 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125853670</v>
+        <v>125855896</v>
       </c>
       <c r="B59" t="n">
-        <v>57654</v>
+        <v>57141</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>667799</v>
+        <v>667767</v>
       </c>
       <c r="R59" t="n">
-        <v>6691867</v>
+        <v>6691898</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6712,22 +6667,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125855905</v>
+        <v>125855897</v>
       </c>
       <c r="B60" t="n">
-        <v>97239</v>
+        <v>57141</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6735,34 +6690,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>667920</v>
+        <v>667812</v>
       </c>
       <c r="R60" t="n">
-        <v>6691730</v>
+        <v>6691902</v>
       </c>
       <c r="S60" t="n">
         <v>12</v>
@@ -6821,10 +6784,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125855903</v>
+        <v>125855899</v>
       </c>
       <c r="B61" t="n">
-        <v>97239</v>
+        <v>57141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6832,34 +6795,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>667902</v>
+        <v>667772</v>
       </c>
       <c r="R61" t="n">
-        <v>6691700</v>
+        <v>6691729</v>
       </c>
       <c r="S61" t="n">
         <v>12</v>
@@ -6892,6 +6863,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färsk spillning. På häll. En del kortklippta med vitt. Eventuellt spelspillning.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6918,10 +6894,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125855919</v>
+        <v>126056867</v>
       </c>
       <c r="B62" t="n">
-        <v>98278</v>
+        <v>57141</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6929,37 +6905,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>667939</v>
+        <v>668108</v>
       </c>
       <c r="R62" t="n">
-        <v>6691772</v>
+        <v>6691849</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7003,60 +6984,65 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125855886</v>
+        <v>127382936</v>
       </c>
       <c r="B63" t="n">
-        <v>91245</v>
+        <v>57141</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>667883</v>
+        <v>668159</v>
       </c>
       <c r="R63" t="n">
-        <v>6691862</v>
+        <v>6691922</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7080,12 +7066,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder av hane, vid vad som såg att vara en balgrop. Även dun.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7100,22 +7091,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125855931</v>
+        <v>125807902</v>
       </c>
       <c r="B64" t="n">
-        <v>100543</v>
+        <v>5179</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7123,21 +7114,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7147,13 +7138,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>667892</v>
+        <v>668094</v>
       </c>
       <c r="R64" t="n">
-        <v>6691878</v>
+        <v>6691828</v>
       </c>
       <c r="S64" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7193,48 +7184,63 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125984239</v>
+        <v>125807903</v>
       </c>
       <c r="B65" t="n">
-        <v>91263</v>
+        <v>5179</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7244,13 +7250,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>667825</v>
+        <v>667990</v>
       </c>
       <c r="R65" t="n">
-        <v>6691849</v>
+        <v>6691886</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7282,61 +7288,71 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Gammal frkp på gren av gammal levande gran</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125984224</v>
+        <v>125807904</v>
       </c>
       <c r="B66" t="n">
-        <v>91245</v>
+        <v>5179</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7346,13 +7362,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>667842</v>
+        <v>667959</v>
       </c>
       <c r="R66" t="n">
-        <v>6691878</v>
+        <v>6691856</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7392,26 +7408,41 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125984240</v>
+        <v>125807905</v>
       </c>
       <c r="B67" t="n">
-        <v>4778</v>
+        <v>5179</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7419,42 +7450,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>667893</v>
+        <v>667721</v>
       </c>
       <c r="R67" t="n">
-        <v>6691840</v>
+        <v>6691796</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7486,11 +7512,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Hål</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7499,26 +7520,41 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125984221</v>
+        <v>127382956</v>
       </c>
       <c r="B68" t="n">
-        <v>91245</v>
+        <v>5178</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7526,37 +7562,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>102204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668119</v>
+        <v>667935</v>
       </c>
       <c r="R68" t="n">
-        <v>6691778</v>
+        <v>6691827</v>
       </c>
       <c r="S68" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7580,12 +7616,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7594,28 +7630,44 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125984218</v>
+        <v>125807890</v>
       </c>
       <c r="B69" t="n">
-        <v>91210</v>
+        <v>4781</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7623,21 +7675,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7647,13 +7699,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>667998</v>
+        <v>668014</v>
       </c>
       <c r="R69" t="n">
-        <v>6691845</v>
+        <v>6691884</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7693,48 +7745,63 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125984234</v>
+        <v>125807891</v>
       </c>
       <c r="B70" t="n">
-        <v>91699</v>
+        <v>4781</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7744,13 +7811,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668124</v>
+        <v>667961</v>
       </c>
       <c r="R70" t="n">
-        <v>6691768</v>
+        <v>6691858</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7790,48 +7857,63 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125984222</v>
+        <v>125807892</v>
       </c>
       <c r="B71" t="n">
-        <v>91245</v>
+        <v>4781</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7841,13 +7923,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668081</v>
+        <v>667736</v>
       </c>
       <c r="R71" t="n">
-        <v>6691773</v>
+        <v>6691854</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7887,26 +7969,41 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125984217</v>
+        <v>125807894</v>
       </c>
       <c r="B72" t="n">
-        <v>91210</v>
+        <v>4781</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7914,21 +8011,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7938,13 +8035,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668042</v>
+        <v>667740</v>
       </c>
       <c r="R72" t="n">
-        <v>6691903</v>
+        <v>6691828</v>
       </c>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7984,48 +8081,63 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125984223</v>
+        <v>125807895</v>
       </c>
       <c r="B73" t="n">
-        <v>91245</v>
+        <v>4781</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8035,13 +8147,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>667997</v>
+        <v>667743</v>
       </c>
       <c r="R73" t="n">
-        <v>6691842</v>
+        <v>6691820</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8081,26 +8193,41 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126056871</v>
+        <v>125807896</v>
       </c>
       <c r="B74" t="n">
-        <v>98278</v>
+        <v>4781</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8108,21 +8235,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8132,10 +8259,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668083</v>
+        <v>667759</v>
       </c>
       <c r="R74" t="n">
-        <v>6691848</v>
+        <v>6691753</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8179,6 +8306,21 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
@@ -8187,17 +8329,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Shanti Wittmar</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126056870</v>
+        <v>125853671</v>
       </c>
       <c r="B75" t="n">
-        <v>4778</v>
+        <v>4781</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8225,17 +8367,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>667807</v>
+        <v>668108</v>
       </c>
       <c r="R75" t="n">
-        <v>6691741</v>
+        <v>6691869</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8275,41 +8417,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Shanti Wittmar</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126056869</v>
+        <v>125853672</v>
       </c>
       <c r="B76" t="n">
-        <v>56584</v>
+        <v>4781</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8317,37 +8444,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>208257</v>
+        <v>102306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>667845</v>
+        <v>667767</v>
       </c>
       <c r="R76" t="n">
-        <v>6691791</v>
+        <v>6691757</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8391,22 +8518,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Shanti Wittmar</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126056867</v>
+        <v>125855913</v>
       </c>
       <c r="B77" t="n">
-        <v>56849</v>
+        <v>4781</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8414,42 +8541,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>102306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668108</v>
+        <v>668200</v>
       </c>
       <c r="R77" t="n">
-        <v>6691849</v>
+        <v>6691772</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8493,22 +8615,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Shanti Wittmar</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127382965</v>
+        <v>125984240</v>
       </c>
       <c r="B78" t="n">
-        <v>91981</v>
+        <v>4781</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8516,37 +8638,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>667915</v>
+        <v>667893</v>
       </c>
       <c r="R78" t="n">
-        <v>6691881</v>
+        <v>6691840</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8570,12 +8697,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Hål</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8586,41 +8718,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127382955</v>
+        <v>126056870</v>
       </c>
       <c r="B79" t="n">
-        <v>105508</v>
+        <v>4781</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8628,43 +8745,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>667920</v>
+        <v>667807</v>
       </c>
       <c r="R79" t="n">
-        <v>6691884</v>
+        <v>6691741</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8691,12 +8799,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8707,6 +8815,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8716,39 +8839,39 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127382962</v>
+        <v>127382958</v>
       </c>
       <c r="B80" t="n">
-        <v>92660</v>
+        <v>4781</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4368</v>
+        <v>102306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8758,10 +8881,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>667935</v>
+        <v>668067</v>
       </c>
       <c r="R80" t="n">
-        <v>6691764</v>
+        <v>6691840</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8804,6 +8927,21 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -8820,32 +8958,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127382956</v>
+        <v>127382959</v>
       </c>
       <c r="B81" t="n">
-        <v>5176</v>
+        <v>4781</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102204</v>
+        <v>102306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8855,10 +8993,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>667935</v>
+        <v>668110</v>
       </c>
       <c r="R81" t="n">
-        <v>6691827</v>
+        <v>6691865</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8899,7 +9037,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8933,10 +9070,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127382930</v>
+        <v>126056869</v>
       </c>
       <c r="B82" t="n">
-        <v>91317</v>
+        <v>56876</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8944,34 +9081,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>208257</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668026</v>
+        <v>667845</v>
       </c>
       <c r="R82" t="n">
-        <v>6691913</v>
+        <v>6691791</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8998,12 +9135,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9014,21 +9151,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9038,17 +9160,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127382959</v>
+        <v>125853674</v>
       </c>
       <c r="B83" t="n">
-        <v>4779</v>
+        <v>99035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9056,37 +9178,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102306</v>
+        <v>219790</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668110</v>
+        <v>668118</v>
       </c>
       <c r="R83" t="n">
-        <v>6691865</v>
+        <v>6691756</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9110,12 +9232,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9126,79 +9248,64 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127382933</v>
+        <v>125853675</v>
       </c>
       <c r="B84" t="n">
-        <v>91352</v>
+        <v>99035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668060</v>
+        <v>668105</v>
       </c>
       <c r="R84" t="n">
-        <v>6691824</v>
+        <v>6691791</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9222,12 +9329,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9238,79 +9345,64 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127382932</v>
+        <v>125855918</v>
       </c>
       <c r="B85" t="n">
-        <v>91352</v>
+        <v>99035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>667928</v>
+        <v>668099</v>
       </c>
       <c r="R85" t="n">
-        <v>6691781</v>
+        <v>6691912</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9334,12 +9426,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9350,41 +9442,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127382938</v>
+        <v>125855919</v>
       </c>
       <c r="B86" t="n">
-        <v>92287</v>
+        <v>99035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,37 +9469,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4769</v>
+        <v>219790</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
         <v>667939</v>
       </c>
       <c r="R86" t="n">
-        <v>6691746</v>
+        <v>6691772</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9446,12 +9523,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9466,22 +9543,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127382953</v>
+        <v>125855921</v>
       </c>
       <c r="B87" t="n">
-        <v>105508</v>
+        <v>99035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9489,37 +9566,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>667945</v>
+        <v>667940</v>
       </c>
       <c r="R87" t="n">
-        <v>6691904</v>
+        <v>6691725</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9543,12 +9620,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9563,22 +9640,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127382944</v>
+        <v>125855922</v>
       </c>
       <c r="B88" t="n">
-        <v>92654</v>
+        <v>99035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9586,37 +9663,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4366</v>
+        <v>219790</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>667983</v>
+        <v>667907</v>
       </c>
       <c r="R88" t="n">
-        <v>6691868</v>
+        <v>6691699</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9640,12 +9717,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9660,22 +9737,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127382952</v>
+        <v>125855924</v>
       </c>
       <c r="B89" t="n">
-        <v>105508</v>
+        <v>99035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9683,37 +9760,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>667937</v>
+        <v>667949</v>
       </c>
       <c r="R89" t="n">
-        <v>6691815</v>
+        <v>6691737</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9737,12 +9814,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9757,22 +9834,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127382966</v>
+        <v>125855925</v>
       </c>
       <c r="B90" t="n">
-        <v>100652</v>
+        <v>99035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9780,37 +9857,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668001</v>
+        <v>667944</v>
       </c>
       <c r="R90" t="n">
-        <v>6691848</v>
+        <v>6691755</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9834,12 +9911,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9854,65 +9931,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127382941</v>
+        <v>125855927</v>
       </c>
       <c r="B91" t="n">
-        <v>57669</v>
+        <v>99035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668038</v>
+        <v>667941</v>
       </c>
       <c r="R91" t="n">
-        <v>6691921</v>
+        <v>6691897</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9936,12 +10008,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9956,60 +10028,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127382951</v>
+        <v>125855929</v>
       </c>
       <c r="B92" t="n">
-        <v>98470</v>
+        <v>99035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>667939</v>
+        <v>667863</v>
       </c>
       <c r="R92" t="n">
-        <v>6691920</v>
+        <v>6691900</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10033,17 +10105,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>1 m väster om stor gran</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10058,22 +10125,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127382929</v>
+        <v>125984242</v>
       </c>
       <c r="B93" t="n">
-        <v>91317</v>
+        <v>99035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10081,37 +10148,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>668059</v>
+        <v>667892</v>
       </c>
       <c r="R93" t="n">
-        <v>6691834</v>
+        <v>6691648</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10135,12 +10202,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10151,41 +10218,26 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127382947</v>
+        <v>126056871</v>
       </c>
       <c r="B94" t="n">
-        <v>91124</v>
+        <v>99035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10193,34 +10245,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3215</v>
+        <v>219790</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>667947</v>
+        <v>668083</v>
       </c>
       <c r="R94" t="n">
-        <v>6691871</v>
+        <v>6691848</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10247,12 +10299,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10272,52 +10324,61 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127382946</v>
+        <v>125807878</v>
       </c>
       <c r="B95" t="n">
-        <v>91124</v>
+        <v>99118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>667937</v>
+        <v>668030</v>
       </c>
       <c r="R95" t="n">
-        <v>6691781</v>
+        <v>6691905</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10344,12 +10405,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Vid stenblock</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10376,32 +10442,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127382957</v>
+        <v>127382951</v>
       </c>
       <c r="B96" t="n">
-        <v>91577</v>
+        <v>99118</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1101</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10411,10 +10477,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>668028</v>
+        <v>667939</v>
       </c>
       <c r="R96" t="n">
-        <v>6691913</v>
+        <v>6691920</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10449,6 +10515,11 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>1 m väster om stor gran</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10457,21 +10528,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -10488,10 +10544,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127382958</v>
+        <v>125807883</v>
       </c>
       <c r="B97" t="n">
-        <v>4779</v>
+        <v>106244</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10499,34 +10555,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102306</v>
+        <v>221144</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668067</v>
+        <v>668026</v>
       </c>
       <c r="R97" t="n">
-        <v>6691840</v>
+        <v>6691901</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10553,12 +10618,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10569,21 +10634,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -10600,10 +10650,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127382945</v>
+        <v>125832167</v>
       </c>
       <c r="B98" t="n">
-        <v>92654</v>
+        <v>106244</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10611,34 +10661,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4366</v>
+        <v>221144</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>667937</v>
+        <v>667940</v>
       </c>
       <c r="R98" t="n">
-        <v>6691815</v>
+        <v>6691828</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10665,12 +10715,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10685,22 +10735,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128260544</v>
+        <v>125855909</v>
       </c>
       <c r="B99" t="n">
-        <v>92439</v>
+        <v>106244</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10708,37 +10758,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4769</v>
+        <v>221144</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>667938</v>
+        <v>667931</v>
       </c>
       <c r="R99" t="n">
-        <v>6691896</v>
+        <v>6691727</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10762,12 +10812,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10782,22 +10832,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128260560</v>
+        <v>127382952</v>
       </c>
       <c r="B100" t="n">
-        <v>91277</v>
+        <v>106244</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10805,21 +10855,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3215</v>
+        <v>221144</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10829,13 +10879,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>667935</v>
+        <v>667937</v>
       </c>
       <c r="R100" t="n">
-        <v>6691779</v>
+        <v>6691815</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10859,12 +10909,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10891,10 +10941,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128260553</v>
+        <v>127382953</v>
       </c>
       <c r="B101" t="n">
-        <v>92806</v>
+        <v>106244</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10902,21 +10952,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4366</v>
+        <v>221144</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10926,13 +10976,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>667943</v>
+        <v>667945</v>
       </c>
       <c r="R101" t="n">
-        <v>6691900</v>
+        <v>6691904</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10956,12 +11006,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10988,32 +11038,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128260589</v>
+        <v>127382954</v>
       </c>
       <c r="B102" t="n">
-        <v>92812</v>
+        <v>106244</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4368</v>
+        <v>221144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11023,13 +11073,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>667928</v>
+        <v>667953</v>
       </c>
       <c r="R102" t="n">
-        <v>6691772</v>
+        <v>6691911</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11053,12 +11103,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11085,10 +11135,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128260545</v>
+        <v>127382955</v>
       </c>
       <c r="B103" t="n">
-        <v>92439</v>
+        <v>106244</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11096,37 +11146,46 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4769</v>
+        <v>221144</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>667945</v>
+        <v>667920</v>
       </c>
       <c r="R103" t="n">
-        <v>6691836</v>
+        <v>6691884</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11150,12 +11209,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11182,10 +11241,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128260547</v>
+        <v>125855900</v>
       </c>
       <c r="B104" t="n">
-        <v>92439</v>
+        <v>97983</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11193,37 +11252,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4769</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>667935</v>
+        <v>668113</v>
       </c>
       <c r="R104" t="n">
-        <v>6691779</v>
+        <v>6691886</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11247,12 +11306,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11267,60 +11326,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128260587</v>
+        <v>125855902</v>
       </c>
       <c r="B105" t="n">
-        <v>90965</v>
+        <v>97983</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3286</v>
+        <v>221945</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>667939</v>
+        <v>667921</v>
       </c>
       <c r="R105" t="n">
-        <v>6691912</v>
+        <v>6691714</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11344,12 +11403,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11364,22 +11423,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128260559</v>
+        <v>125855903</v>
       </c>
       <c r="B106" t="n">
-        <v>91277</v>
+        <v>97983</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11387,37 +11446,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>667946</v>
+        <v>667902</v>
       </c>
       <c r="R106" t="n">
-        <v>6691856</v>
+        <v>6691700</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11441,12 +11500,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11461,68 +11520,60 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132917305</v>
+        <v>125855905</v>
       </c>
       <c r="B107" t="n">
-        <v>57955</v>
+        <v>97983</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Movisen V, Valö, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>667801</v>
+        <v>667920</v>
       </c>
       <c r="R107" t="n">
-        <v>6691915</v>
+        <v>6691730</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11546,22 +11597,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11576,68 +11617,60 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132917355</v>
+        <v>125807906</v>
       </c>
       <c r="B108" t="n">
-        <v>57955</v>
+        <v>101326</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Movisen V2, Valö, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>667794</v>
+        <v>667888</v>
       </c>
       <c r="R108" t="n">
-        <v>6691808</v>
+        <v>6691884</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11661,22 +11694,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11691,15 +11714,500 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>125807907</v>
+      </c>
+      <c r="B109" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>667915</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6691893</v>
+      </c>
+      <c r="S109" t="n">
+        <v>15</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>125832173</v>
+      </c>
+      <c r="B110" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>668118</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6691903</v>
+      </c>
+      <c r="S110" t="n">
+        <v>15</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>125855930</v>
+      </c>
+      <c r="B111" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>667952</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6691797</v>
+      </c>
+      <c r="S111" t="n">
+        <v>12</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>125855931</v>
+      </c>
+      <c r="B112" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>667892</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6691878</v>
+      </c>
+      <c r="S112" t="n">
+        <v>12</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>127382966</v>
+      </c>
+      <c r="B113" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>668001</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6691848</v>
+      </c>
+      <c r="S113" t="n">
+        <v>15</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19250-2026 artfynd.xlsx
+++ b/artfynd/A 19250-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AZ113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807855</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807884</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807870</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807871</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382957</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807858</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807859</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807861</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807862</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1775,6 +1825,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807863</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807864</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125832163</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2081,6 +2146,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855884</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2178,6 +2248,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855886</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2275,6 +2350,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984221</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2372,6 +2452,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984222</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2469,6 +2554,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984223</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2566,6 +2656,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984224</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2678,6 +2773,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382932</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2790,6 +2890,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382933</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2887,6 +2992,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984234</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2999,6 +3109,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382965</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3096,6 +3211,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382946</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3193,6 +3313,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382947</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3290,6 +3415,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260559</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3387,6 +3517,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260560</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3484,6 +3619,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260587</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3581,6 +3721,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382944</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3678,6 +3823,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382945</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3775,6 +3925,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260553</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3872,6 +4027,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382962</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3969,6 +4129,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260589</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4066,6 +4231,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382938</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4163,6 +4333,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260544</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4260,6 +4435,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260545</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4357,6 +4537,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260547</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4469,6 +4654,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807857</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4566,6 +4756,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984217</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4663,6 +4858,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984218</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4775,6 +4975,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382929</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4887,6 +5092,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382930</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4999,6 +5209,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807879</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5111,6 +5326,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807880</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5223,6 +5443,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807881</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5335,6 +5560,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807882</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5432,6 +5662,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125832166</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5529,6 +5764,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125832160</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5631,6 +5871,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121373647</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5728,6 +5973,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853669</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5825,6 +6075,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853670</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5927,6 +6182,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382941</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6042,6 +6302,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917305</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6157,6 +6422,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917355</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6254,6 +6524,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125832164</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6356,6 +6631,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125832165</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6466,6 +6746,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855892</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6571,6 +6856,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855894</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6676,6 +6966,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855896</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6781,6 +7076,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855897</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6891,6 +7191,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855899</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6993,6 +7298,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126056867</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7100,6 +7410,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382936</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7212,6 +7527,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807902</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7324,6 +7644,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807903</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7436,6 +7761,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807904</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7548,6 +7878,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807905</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7661,6 +7996,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382956</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7773,6 +8113,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807890</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7885,6 +8230,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807891</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7997,6 +8347,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807892</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8109,6 +8464,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807894</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8221,6 +8581,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807895</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8333,6 +8698,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807896</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8430,6 +8800,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853671</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8527,6 +8902,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853672</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8624,6 +9004,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855913</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8731,6 +9116,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984240</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8843,6 +9233,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126056870</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8955,6 +9350,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382958</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9067,6 +9467,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382959</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9164,6 +9569,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126056869</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9261,6 +9671,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853674</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9358,6 +9773,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853675</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9455,6 +9875,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855918</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9552,6 +9977,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855919</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9649,6 +10079,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855921</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9746,6 +10181,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855922</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9843,6 +10283,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855924</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9940,6 +10385,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855925</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10037,6 +10487,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855927</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10134,6 +10589,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855929</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10231,6 +10691,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984242</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10328,6 +10793,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126056871</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10439,6 +10909,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807878</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10541,6 +11016,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382951</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10647,6 +11127,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807883</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10744,6 +11229,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125832167</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10841,6 +11331,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855909</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10938,6 +11433,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382952</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11035,6 +11535,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382953</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11132,6 +11637,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382954</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11238,6 +11748,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382955</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11335,6 +11850,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855900</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11432,6 +11952,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855902</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11529,6 +12054,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855903</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11626,6 +12156,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855905</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11723,6 +12258,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807906</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11820,6 +12360,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807907</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11917,6 +12462,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125832173</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12014,6 +12564,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855930</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12111,6 +12666,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855931</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12208,8 +12768,127 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382966</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>